--- a/site/downloads/files/briefings/cvd_cases_2023_v1/workbook/bnr_cvd_cases_2023_v1.xlsx
+++ b/site/downloads/files/briefings/cvd_cases_2023_v1/workbook/bnr_cvd_cases_2023_v1.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="390" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="396" uniqueCount="117">
   <si>
     <t>field</t>
   </si>
@@ -30,10 +30,13 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Target year</t>
-  </si>
-  <si>
-    <t>Baseline period</t>
+    <t>Output type</t>
+  </si>
+  <si>
+    <t>Domain</t>
+  </si>
+  <si>
+    <t>Surveillance area</t>
   </si>
   <si>
     <t>Registry</t>
@@ -42,6 +45,12 @@
     <t>Geography</t>
   </si>
   <si>
+    <t>Period</t>
+  </si>
+  <si>
+    <t>Release date</t>
+  </si>
+  <si>
     <t>Contents</t>
   </si>
   <si>
@@ -57,28 +66,37 @@
     <t>cvd_cases_2023_v1</t>
   </si>
   <si>
-    <t>Hospital cardiovascular cases in Barbados, 2023</t>
+    <t>CVD cases in Barbados, 2023</t>
+  </si>
+  <si>
+    <t>briefing</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>CVD</t>
+  </si>
+  <si>
+    <t>BNR-CVD</t>
+  </si>
+  <si>
+    <t>Barbados</t>
   </si>
   <si>
     <t>2023</t>
   </si>
   <si>
-    <t>2018-2022</t>
-  </si>
-  <si>
-    <t>BNR-CVD</t>
-  </si>
-  <si>
-    <t>Barbados</t>
+    <t>2026-05-15</t>
   </si>
   <si>
     <t>Data sheets, dataset metadata sheets, and variable metadata sheets</t>
   </si>
   <si>
-    <t>Aggregate hospital-ascertained case counts</t>
-  </si>
-  <si>
-    <t>Counts should not be interpreted as population incidence</t>
+    <t>Aggregate hospital-ascertained case counts.</t>
+  </si>
+  <si>
+    <t>Counts describe hospital-ascertained cases and should not be interpreted as population incidence.</t>
   </si>
   <si>
     <t>etype</t>
@@ -190,9 +208,6 @@
   </si>
   <si>
     <t>Weekly and cumulative hospital-ascertained stroke and heart attack case counts for 2023 compared with the 2018-2022 annual average.</t>
-  </si>
-  <si>
-    <t>Counts describe hospital-ascertained cases and should not be interpreted as population incidence.</t>
   </si>
   <si>
     <t>en</t>
@@ -400,7 +415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -408,7 +423,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
@@ -416,7 +431,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -424,7 +439,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -432,7 +447,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -440,7 +455,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -448,7 +463,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -456,7 +471,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -464,7 +479,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -472,7 +487,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -480,7 +495,31 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -494,30 +533,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -540,7 +579,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -563,7 +602,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
@@ -586,7 +625,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B5" s="1">
         <v>4</v>
@@ -609,7 +648,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B6" s="1">
         <v>5</v>
@@ -632,7 +671,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B7" s="1">
         <v>6</v>
@@ -655,7 +694,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B8" s="1">
         <v>7</v>
@@ -678,7 +717,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1">
         <v>8</v>
@@ -701,7 +740,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1">
         <v>9</v>
@@ -724,7 +763,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1">
         <v>10</v>
@@ -747,7 +786,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B12" s="1">
         <v>11</v>
@@ -770,7 +809,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B13" s="1">
         <v>12</v>
@@ -793,7 +832,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B14" s="1">
         <v>13</v>
@@ -816,7 +855,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B15" s="1">
         <v>14</v>
@@ -839,7 +878,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B16" s="1">
         <v>15</v>
@@ -862,7 +901,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B17" s="1">
         <v>16</v>
@@ -885,7 +924,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B18" s="1">
         <v>17</v>
@@ -908,7 +947,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1">
         <v>18</v>
@@ -931,7 +970,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1">
         <v>19</v>
@@ -954,7 +993,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1">
         <v>20</v>
@@ -977,7 +1016,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B22" s="1">
         <v>21</v>
@@ -1000,7 +1039,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B23" s="1">
         <v>22</v>
@@ -1023,7 +1062,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B24" s="1">
         <v>23</v>
@@ -1046,7 +1085,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B25" s="1">
         <v>24</v>
@@ -1069,7 +1108,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B26" s="1">
         <v>25</v>
@@ -1092,7 +1131,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B27" s="1">
         <v>26</v>
@@ -1115,7 +1154,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B28" s="1">
         <v>27</v>
@@ -1138,7 +1177,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B29" s="1">
         <v>28</v>
@@ -1161,7 +1200,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B30" s="1">
         <v>29</v>
@@ -1184,7 +1223,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B31" s="1">
         <v>30</v>
@@ -1207,7 +1246,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B32" s="1">
         <v>31</v>
@@ -1230,7 +1269,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B33" s="1">
         <v>32</v>
@@ -1253,7 +1292,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B34" s="1">
         <v>33</v>
@@ -1276,7 +1315,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B35" s="1">
         <v>34</v>
@@ -1299,7 +1338,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B36" s="1">
         <v>35</v>
@@ -1322,7 +1361,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B37" s="1">
         <v>36</v>
@@ -1345,7 +1384,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B38" s="1">
         <v>37</v>
@@ -1368,7 +1407,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B39" s="1">
         <v>38</v>
@@ -1391,7 +1430,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B40" s="1">
         <v>39</v>
@@ -1414,7 +1453,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B41" s="1">
         <v>40</v>
@@ -1437,7 +1476,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B42" s="1">
         <v>41</v>
@@ -1460,7 +1499,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B43" s="1">
         <v>42</v>
@@ -1483,7 +1522,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B44" s="1">
         <v>43</v>
@@ -1506,7 +1545,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B45" s="1">
         <v>44</v>
@@ -1529,7 +1568,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B46" s="1">
         <v>45</v>
@@ -1552,7 +1591,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B47" s="1">
         <v>46</v>
@@ -1575,7 +1614,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B48" s="1">
         <v>47</v>
@@ -1598,7 +1637,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B49" s="1">
         <v>48</v>
@@ -1621,7 +1660,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B50" s="1">
         <v>49</v>
@@ -1644,7 +1683,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B51" s="1">
         <v>50</v>
@@ -1667,7 +1706,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B52" s="1">
         <v>51</v>
@@ -1690,7 +1729,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B53" s="1">
         <v>52</v>
@@ -1713,7 +1752,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B54" s="1">
         <v>1</v>
@@ -1736,7 +1775,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B55" s="1">
         <v>2</v>
@@ -1759,7 +1798,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B56" s="1">
         <v>3</v>
@@ -1782,7 +1821,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B57" s="1">
         <v>4</v>
@@ -1805,7 +1844,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B58" s="1">
         <v>5</v>
@@ -1828,7 +1867,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B59" s="1">
         <v>6</v>
@@ -1851,7 +1890,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B60" s="1">
         <v>7</v>
@@ -1874,7 +1913,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B61" s="1">
         <v>8</v>
@@ -1897,7 +1936,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B62" s="1">
         <v>9</v>
@@ -1920,7 +1959,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B63" s="1">
         <v>10</v>
@@ -1943,7 +1982,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B64" s="1">
         <v>11</v>
@@ -1966,7 +2005,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B65" s="1">
         <v>12</v>
@@ -1989,7 +2028,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B66" s="1">
         <v>13</v>
@@ -2012,7 +2051,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B67" s="1">
         <v>14</v>
@@ -2035,7 +2074,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B68" s="1">
         <v>15</v>
@@ -2058,7 +2097,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B69" s="1">
         <v>16</v>
@@ -2081,7 +2120,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B70" s="1">
         <v>17</v>
@@ -2104,7 +2143,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B71" s="1">
         <v>18</v>
@@ -2127,7 +2166,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B72" s="1">
         <v>19</v>
@@ -2150,7 +2189,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B73" s="1">
         <v>20</v>
@@ -2173,7 +2212,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B74" s="1">
         <v>21</v>
@@ -2196,7 +2235,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B75" s="1">
         <v>22</v>
@@ -2219,7 +2258,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B76" s="1">
         <v>23</v>
@@ -2242,7 +2281,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B77" s="1">
         <v>24</v>
@@ -2265,7 +2304,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B78" s="1">
         <v>25</v>
@@ -2288,7 +2327,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B79" s="1">
         <v>26</v>
@@ -2311,7 +2350,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B80" s="1">
         <v>27</v>
@@ -2334,7 +2373,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B81" s="1">
         <v>28</v>
@@ -2357,7 +2396,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B82" s="1">
         <v>29</v>
@@ -2380,7 +2419,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B83" s="1">
         <v>30</v>
@@ -2403,7 +2442,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B84" s="1">
         <v>31</v>
@@ -2426,7 +2465,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B85" s="1">
         <v>32</v>
@@ -2449,7 +2488,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B86" s="1">
         <v>33</v>
@@ -2472,7 +2511,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B87" s="1">
         <v>34</v>
@@ -2495,7 +2534,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B88" s="1">
         <v>35</v>
@@ -2518,7 +2557,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B89" s="1">
         <v>36</v>
@@ -2541,7 +2580,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B90" s="1">
         <v>37</v>
@@ -2564,7 +2603,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B91" s="1">
         <v>38</v>
@@ -2587,7 +2626,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B92" s="1">
         <v>39</v>
@@ -2610,7 +2649,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B93" s="1">
         <v>40</v>
@@ -2633,7 +2672,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B94" s="1">
         <v>41</v>
@@ -2656,7 +2695,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B95" s="1">
         <v>42</v>
@@ -2679,7 +2718,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B96" s="1">
         <v>43</v>
@@ -2702,7 +2741,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B97" s="1">
         <v>44</v>
@@ -2725,7 +2764,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B98" s="1">
         <v>45</v>
@@ -2748,7 +2787,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B99" s="1">
         <v>46</v>
@@ -2771,7 +2810,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B100" s="1">
         <v>47</v>
@@ -2794,7 +2833,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B101" s="1">
         <v>48</v>
@@ -2817,7 +2856,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B102" s="1">
         <v>49</v>
@@ -2840,7 +2879,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B103" s="1">
         <v>50</v>
@@ -2863,7 +2902,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B104" s="1">
         <v>51</v>
@@ -2886,7 +2925,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B105" s="1">
         <v>52</v>
@@ -2918,200 +2957,200 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -3125,186 +3164,186 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
         <v>30</v>
       </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F4" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" t="s">
         <v>76</v>
-      </c>
-      <c r="G5" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E8" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F8" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G8" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -3318,39 +3357,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
         <v>116.59999999999999</v>
@@ -3364,16 +3403,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" t="s">
         <v>21</v>
-      </c>
-      <c r="B3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
       </c>
       <c r="E3" s="1">
         <v>120</v>
@@ -3387,16 +3426,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1">
         <v>155.80000000000001</v>
@@ -3410,16 +3449,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" t="s">
         <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
       </c>
       <c r="E5" s="1">
         <v>168</v>
@@ -3433,16 +3472,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1">
         <v>50.600000000000001</v>
@@ -3456,16 +3495,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E7" s="1">
         <v>52</v>
@@ -3479,16 +3518,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1">
         <v>91.200000000000003</v>
@@ -3502,16 +3541,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E9" s="1">
         <v>89</v>
@@ -3534,200 +3573,200 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -3741,186 +3780,186 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F5" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G5" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F6" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F7" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E8" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F8" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G8" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
